--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:42</t>
+    <t xml:space="preserve">2026-09-10 00:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:50</t>
+    <t xml:space="preserve">2026-09-18 10:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:59</t>
+    <t xml:space="preserve">2026-09-23 14:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:20</t>
+    <t xml:space="preserve">2026-10-02 15:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_biobio.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Penco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Laja</t>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Yumbel</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Curanilahue</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:26</t>
+    <t xml:space="preserve">2026-10-04 10:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:03</t>
+    <t xml:space="preserve">2026-10-05 14:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
